--- a/RawSourcesDetection/output/raw_sources_test_connections.xlsx
+++ b/RawSourcesDetection/output/raw_sources_test_connections.xlsx
@@ -13,6 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing Files" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matched Vectors" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched Vectors" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dynamic References" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stale Links" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +50,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +97,11 @@
         <fgColor rgb="00FFEBEE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -117,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +177,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -532,10 +554,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -570,7 +592,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sheet1, Inputs, Formulas</t>
+          <t>Sheet1, Inputs</t>
         </is>
       </c>
     </row>
@@ -750,7 +772,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -798,7 +820,79 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>── Extra Scanners ──</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic INDIRECT refs</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RTD (live feed) refs</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Stale / phantom links</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>XLSB files (limited scan)</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Manager entries</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -816,15 +910,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1219,12 +1313,12 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>external_workbook</t>
+          <t>unc_path</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>source_data.xlsx</t>
+          <t>\\fileserver\share\</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -1239,88 +1333,88 @@
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>Sheet1!A10</t>
+          <t>Sheet1!A11</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>unc_path</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>\\fileserver\share\</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>webservice</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>https://api.exchangerate.host/latest</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Sheet1!A11</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>test_connections.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Sheet1!A12</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>webservice</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>https://api.exchangerate.host/latest</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>bloomberg</t>
+        </is>
+      </c>
+      <c r="C15" s="14">
+        <f>BDP("AAPL US Equity","PX_LAST")</f>
+        <v/>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>Sheet1!A12</t>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>test_connections.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>Sheet1!A13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>formula</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>bloomberg</t>
-        </is>
-      </c>
-      <c r="C16" s="14">
-        <f>BDP("AAPL US Equity","PX_LAST")</f>
-        <v/>
+          <t>external_workbook</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>external_source.xlsx</t>
+        </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
@@ -1334,7 +1428,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Sheet1!A13</t>
+          <t>HiddenData!A1</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1440,12 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>external_workbook</t>
+          <t>sharepoint_workbook</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>external_source.xlsx</t>
+          <t>https://mycompany.sharepoint.com/sites/Finance/Shared Documents/budget_2024.xlsx</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -1366,39 +1460,39 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>HiddenData!A1</t>
+          <t>xl/externalLinks/externalLink1.xml</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>sharepoint_workbook</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>https://mycompany.sharepoint.com/sites/Finance/Shared Documents/budget_2024.xlsx</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>hyperlink</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>https://example.com/data-source</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>xl/externalLinks/externalLink1.xml</t>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>test_connections.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Sheet1:A5</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1504,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>http</t>
+          <t>file_url</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>https://example.com/data-source</t>
+          <t>file:///C:/data/source_data.xlsx</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
@@ -1430,551 +1524,103 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Sheet1:A5</t>
+          <t>Sheet1:A6</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>file</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>named_range_external</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>budget.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>test_connections.xlsx</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>workbook.xml:definedNames</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>hyperlink</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>file_url</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>file:///C:/data/source_data.xlsx</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>comment_url</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>https://api.data.gov/economic/v1/stats</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>Sheet1:A6</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>test_connections.xlsx</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Sheet1:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>named_range_external</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>budget.xlsx</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>unc_path</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>\\fileserver\reports\quarterly.xlsx</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>workbook.xml:definedNames</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>hyperlink</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>comment_url</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>https://api.data.gov/economic/v1/stats</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>test_connections.xlsx</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Sheet1:comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>unc_path</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>\\fileserver\reports\quarterly.xlsx</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>Sheet1:comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>metadata</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>core_properties</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>docProps/core.xml</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>docProps/core.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>metadata</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>app_properties</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>docProps/app.xml</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>docProps/app.xml</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>metadata</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>custom_property_file_path</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>\\fileserver\shared\datasets\master_data.xlsx</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>docProps/custom.xml:DataSourcePath</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>metadata</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>custom_property_url</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>https://reporting.corp.local/api/v2/reports</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>docProps/custom.xml:ReportingServer</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>hardcoded_value</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Sheet1!B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>source_note</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>Source: Bloomberg as of 12/31/2024</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Inputs!C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>source_note</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>Per FactSet consensus estimates</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Inputs!C3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>source_note</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>Source: Company filings 2023</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Inputs!C4</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>source_note</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>Data from Reuters</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>Inputs!C5</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>hardcoded_value</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>0.085</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>Inputs!B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>hardcoded_value</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>0.025</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>Inputs!B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>hardcoded_value</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Inputs!B4</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>input</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>hardcoded_value</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>1234.5</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>test_connections.xlsx</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>Inputs!B5</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2000,7 +1646,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2046,6 +1693,11 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
+          <t>Ref Origin</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
           <t>Resolved Path</t>
         </is>
       </c>
@@ -2091,7 +1743,12 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>/home/nitish/Documents/github/ExcelLineageDetector/expt/source_data.xlsx</t>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>/home/nitish/Documents/github/ExcelLineageDetector/RawSourcesDetection/inputs/source_data.xlsx</t>
         </is>
       </c>
     </row>
@@ -2136,7 +1793,12 @@
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>/home/nitish/Documents/github/ExcelLineageDetector/expt/quarterly.xlsx</t>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>/home/nitish/Documents/github/ExcelLineageDetector/RawSourcesDetection/inputs/quarterly.xlsx</t>
         </is>
       </c>
     </row>
@@ -2151,7 +1813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2159,6 +1821,7 @@
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2187,6 +1850,11 @@
           <t>Cells Referencing (first 10)</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Transitive Unknown</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -2212,6 +1880,11 @@
           <t>Sheet1!A10</t>
         </is>
       </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>YES — all dependencies of this file are invisible until it is supplied</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -2235,6 +1908,11 @@
       <c r="E3" s="18" t="inlineStr">
         <is>
           <t>Sheet1!A11</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>YES — all dependencies of this file are invisible until it is supplied</t>
         </is>
       </c>
     </row>
@@ -2327,14 +2005,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2355,12 +2035,117 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>Column Header</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Row Label</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>Sample Values (first 5)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Action Required</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>No dynamic references detected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Stale Linked File</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>test_connections.xlsx</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="inlineStr">
+        <is>
+          <t>budget_2024.xlsx</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>Remove via Excel → Data → Edit Links → Break Link. File is registered but not referenced by any formula.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>No Excel Scenario Manager entries detected.</t>
         </is>
       </c>
     </row>
